--- a/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
@@ -14,6 +14,7 @@
     <col min="2" max="2" width="12"/>
     <col min="3" max="3" width="22"/>
     <col min="4" max="4" width="75"/>
+    <col min="5" max="5" width="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37,6 +38,11 @@
           <t xml:space="preserve">Описание</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ссылка на фото</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -57,6 +63,11 @@
           <t xml:space="preserve">Установка импланта Osstem (Южная Корея) «под ключ». Хирург-имплантолог, стаж 15 лет. Гарантия 10 лет. Цена «от».</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -77,6 +88,11 @@
           <t xml:space="preserve">Установка импланта Dentium (Южная Корея). КТ и план лечения бесплатно при заключении договора. Цена «от».</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -97,6 +113,11 @@
           <t xml:space="preserve">Премиум-имплант Straumann (Швейцария). Гарантия 10 лет. Цена «от».</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -117,6 +138,11 @@
           <t xml:space="preserve">Имплантация с металлокерамической коронкой под ключ. Цена «от».</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -137,6 +163,11 @@
           <t xml:space="preserve">Имплантация с циркониевой коронкой под ключ. Цена «от».</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -157,6 +188,11 @@
           <t xml:space="preserve">Несъёмный протез всей челюсти на 4 имплантах. Цена «от», за одну челюсть.</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -177,6 +213,11 @@
           <t xml:space="preserve">Несъёмный протез всей челюсти на 6 имплантах. Цена «от», за одну челюсть.</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -197,6 +238,11 @@
           <t xml:space="preserve">Металлические, керамические или сапфировые брекеты под ключ. Стаж ортодонта 15 лет. Цена «от».</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/orthodontics.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -217,6 +263,11 @@
           <t xml:space="preserve">Прозрачные элайнеры, полный курс исправления прикуса. Цена «от».</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/orthodontics.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -237,6 +288,11 @@
           <t xml:space="preserve">Первичная консультация ортодонта с расчётом ТРГ — бесплатно. Подберём брекеты или элайнеры.</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-ortho-free.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -257,6 +313,11 @@
           <t xml:space="preserve">Лечение кариеса за одно посещение, анестезия включена. Цена «от».</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/caries-treatment.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -277,6 +338,11 @@
           <t xml:space="preserve">Лечение пульпита одноканального зуба. Цена «от».</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/caries-treatment.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -297,6 +363,11 @@
           <t xml:space="preserve">Эндодонтическое лечение каналов под микроскопом. Цена «от».</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/caries-treatment.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -317,6 +388,11 @@
           <t xml:space="preserve">Эстетическая реставрация переднего зуба. Цена «от».</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/caries-treatment.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -337,6 +413,11 @@
           <t xml:space="preserve">Простое и сложное удаление зуба, под анестезией. Цена «от».</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/surgery.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -357,6 +438,11 @@
           <t xml:space="preserve">Удаление ретинированного зуба мудрости опытным хирургом. Цена «от».</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/surgery.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -377,6 +463,11 @@
           <t xml:space="preserve">Наращивание костной ткани. Цена «от».</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/surgery.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -397,6 +488,11 @@
           <t xml:space="preserve">Закрытый синус-лифтинг для имплантации на верхней челюсти. Цена «от».</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/surgery.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -417,6 +513,11 @@
           <t xml:space="preserve">Металлокерамическая коронка. Цена «от».</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/prosthetics.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -437,6 +538,11 @@
           <t xml:space="preserve">Монолитная циркониевая коронка. Цена «от».</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/prosthetics.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -457,6 +563,11 @@
           <t xml:space="preserve">Коронка из дисиликата лития E-max (эстетика). Цена «от».</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/prosthetics.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -477,6 +588,11 @@
           <t xml:space="preserve">Полный съёмный акриловый протез на одну челюсть. Цена «от».</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/prosthetics.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -497,6 +613,11 @@
           <t xml:space="preserve">Бюгельный протез на замках. Цена «от».</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/prosthetics.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -517,6 +638,11 @@
           <t xml:space="preserve">Керамический винир E-max. Голливудская улыбка за 2 визита. Цена «от».</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/veneers.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -537,6 +663,11 @@
           <t xml:space="preserve">Ультратонкий люминир Cerinate без обточки. Цена «от».</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/veneers.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -557,6 +688,11 @@
           <t xml:space="preserve">Композитный винир (прямая реставрация). Цена «от».</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/veneers.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -577,6 +713,11 @@
           <t xml:space="preserve">Комплекс из 10 виниров E-max под ключ. Цена «от».</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/veneers.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -597,6 +738,11 @@
           <t xml:space="preserve">Профессиональная чистка зубов: ультразвук, Air Flow, полировка, фторирование.</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/hygiene.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -617,6 +763,11 @@
           <t xml:space="preserve">Чистка Air Flow — удаление налёта и пигмента.</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/hygiene.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -637,6 +788,11 @@
           <t xml:space="preserve">Vector-терапия при пародонтите, 1 челюсть. Цена «от».</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/periodontology.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -657,6 +813,11 @@
           <t xml:space="preserve">Плазмолифтинг дёсен, 1 пробирка. Цена «от».</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/periodontology.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -677,6 +838,11 @@
           <t xml:space="preserve">Лечение кариеса молочного зуба у детей с 2 лет, в игровой форме. Цена «от».</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/pediatric.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -697,6 +863,11 @@
           <t xml:space="preserve">Лечение молочного зуба с цветной пломбой Twinky Star. Цена «от».</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/pediatric.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -717,6 +888,11 @@
           <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/pediatric.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -737,6 +913,11 @@
           <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-ct-plan.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -757,6 +938,11 @@
           <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-whitening.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -777,6 +963,11 @@
           <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-implant-gift.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -797,6 +988,11 @@
           <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-cleaning-gift.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -817,6 +1013,11 @@
           <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-benefits.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -835,6 +1036,11 @@
       <c r="D41" t="inlineStr">
         <is>
           <t xml:space="preserve">Скидка от 3% до 10% всем членам семьи при лечении 3 и более человек.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-family.jpg</t>
         </is>
       </c>
     </row>

--- a/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
@@ -38,11 +38,6 @@
           <t xml:space="preserve">Описание</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ссылка на фото</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -63,11 +58,6 @@
           <t xml:space="preserve">Установка импланта Osstem (Южная Корея) «под ключ». Хирург-имплантолог, стаж 15 лет. Гарантия 10 лет. Цена «от».</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -88,11 +78,6 @@
           <t xml:space="preserve">Установка импланта Dentium (Южная Корея). КТ и план лечения бесплатно при заключении договора. Цена «от».</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -113,11 +98,6 @@
           <t xml:space="preserve">Премиум-имплант Straumann (Швейцария). Гарантия 10 лет. Цена «от».</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -138,11 +118,6 @@
           <t xml:space="preserve">Имплантация с металлокерамической коронкой под ключ. Цена «от».</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -163,11 +138,6 @@
           <t xml:space="preserve">Имплантация с циркониевой коронкой под ключ. Цена «от».</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -188,11 +158,6 @@
           <t xml:space="preserve">Несъёмный протез всей челюсти на 4 имплантах. Цена «от», за одну челюсть.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -213,11 +178,6 @@
           <t xml:space="preserve">Несъёмный протез всей челюсти на 6 имплантах. Цена «от», за одну челюсть.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/implant.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -238,11 +198,6 @@
           <t xml:space="preserve">Металлические, керамические или сапфировые брекеты под ключ. Стаж ортодонта 15 лет. Цена «от».</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/orthodontics.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -263,11 +218,6 @@
           <t xml:space="preserve">Прозрачные элайнеры, полный курс исправления прикуса. Цена «от».</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/orthodontics.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -275,9 +225,7 @@
           <t xml:space="preserve">Бесплатная консультация ортодонта</t>
         </is>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
+      <c r="B11"/>
       <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ортодонтия</t>
@@ -286,11 +234,6 @@
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">Первичная консультация ортодонта с расчётом ТРГ — бесплатно. Подберём брекеты или элайнеры.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-ortho-free.jpg</t>
         </is>
       </c>
     </row>
@@ -313,11 +256,6 @@
           <t xml:space="preserve">Лечение кариеса за одно посещение, анестезия включена. Цена «от».</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/caries-treatment.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -338,11 +276,6 @@
           <t xml:space="preserve">Лечение пульпита одноканального зуба. Цена «от».</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/caries-treatment.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -363,11 +296,6 @@
           <t xml:space="preserve">Эндодонтическое лечение каналов под микроскопом. Цена «от».</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/caries-treatment.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -388,11 +316,6 @@
           <t xml:space="preserve">Эстетическая реставрация переднего зуба. Цена «от».</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/caries-treatment.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -413,11 +336,6 @@
           <t xml:space="preserve">Простое и сложное удаление зуба, под анестезией. Цена «от».</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/surgery.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -438,11 +356,6 @@
           <t xml:space="preserve">Удаление ретинированного зуба мудрости опытным хирургом. Цена «от».</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/surgery.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -463,11 +376,6 @@
           <t xml:space="preserve">Наращивание костной ткани. Цена «от».</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/surgery.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -488,11 +396,6 @@
           <t xml:space="preserve">Закрытый синус-лифтинг для имплантации на верхней челюсти. Цена «от».</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/surgery.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -513,11 +416,6 @@
           <t xml:space="preserve">Металлокерамическая коронка. Цена «от».</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/prosthetics.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -538,11 +436,6 @@
           <t xml:space="preserve">Монолитная циркониевая коронка. Цена «от».</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/prosthetics.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -563,11 +456,6 @@
           <t xml:space="preserve">Коронка из дисиликата лития E-max (эстетика). Цена «от».</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/prosthetics.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -588,11 +476,6 @@
           <t xml:space="preserve">Полный съёмный акриловый протез на одну челюсть. Цена «от».</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/prosthetics.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -613,11 +496,6 @@
           <t xml:space="preserve">Бюгельный протез на замках. Цена «от».</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/prosthetics.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -638,11 +516,6 @@
           <t xml:space="preserve">Керамический винир E-max. Голливудская улыбка за 2 визита. Цена «от».</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/veneers.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -663,11 +536,6 @@
           <t xml:space="preserve">Ультратонкий люминир Cerinate без обточки. Цена «от».</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/veneers.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -688,11 +556,6 @@
           <t xml:space="preserve">Композитный винир (прямая реставрация). Цена «от».</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/veneers.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -713,11 +576,6 @@
           <t xml:space="preserve">Комплекс из 10 виниров E-max под ключ. Цена «от».</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/veneers.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -738,11 +596,6 @@
           <t xml:space="preserve">Профессиональная чистка зубов: ультразвук, Air Flow, полировка, фторирование.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/hygiene.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -763,11 +616,6 @@
           <t xml:space="preserve">Чистка Air Flow — удаление налёта и пигмента.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/hygiene.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -788,11 +636,6 @@
           <t xml:space="preserve">Vector-терапия при пародонтите, 1 челюсть. Цена «от».</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/periodontology.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -813,11 +656,6 @@
           <t xml:space="preserve">Плазмолифтинг дёсен, 1 пробирка. Цена «от».</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/periodontology.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -838,11 +676,6 @@
           <t xml:space="preserve">Лечение кариеса молочного зуба у детей с 2 лет, в игровой форме. Цена «от».</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/pediatric.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -863,11 +696,6 @@
           <t xml:space="preserve">Лечение молочного зуба с цветной пломбой Twinky Star. Цена «от».</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/pediatric.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -888,11 +716,6 @@
           <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/pediatric.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -913,11 +736,6 @@
           <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-ct-plan.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -938,11 +756,6 @@
           <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-whitening.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -950,9 +763,7 @@
           <t xml:space="preserve">Акция: каждый 3-й имплант в подарок</t>
         </is>
       </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
+      <c r="B38"/>
       <c r="C38" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
@@ -961,11 +772,6 @@
       <c r="D38" t="inlineStr">
         <is>
           <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-implant-gift.jpg</t>
         </is>
       </c>
     </row>
@@ -975,9 +781,7 @@
           <t xml:space="preserve">Акция: чистка в подарок при имплантации или брекетах</t>
         </is>
       </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
+      <c r="B39"/>
       <c r="C39" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
@@ -986,11 +790,6 @@
       <c r="D39" t="inlineStr">
         <is>
           <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-cleaning-gift.jpg</t>
         </is>
       </c>
     </row>
@@ -1000,9 +799,7 @@
           <t xml:space="preserve">Скидка 10% пенсионерам, многодетным и военнослужащим</t>
         </is>
       </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
+      <c r="B40"/>
       <c r="C40" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
@@ -1011,11 +808,6 @@
       <c r="D40" t="inlineStr">
         <is>
           <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-benefits.jpg</t>
         </is>
       </c>
     </row>
@@ -1025,9 +817,7 @@
           <t xml:space="preserve">Семейная программа — скидка 3–10%</t>
         </is>
       </c>
-      <c r="B41">
-        <v>0</v>
-      </c>
+      <c r="B41"/>
       <c r="C41" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
@@ -1036,11 +826,6 @@
       <c r="D41" t="inlineStr">
         <is>
           <t xml:space="preserve">Скидка от 3% до 10% всем членам семьи при лечении 3 и более человек.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://angel-denta.ru/assets/img/yb/promo-family.jpg</t>
         </is>
       </c>
     </row>

--- a/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
@@ -320,11 +320,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удаление зуба</t>
+          <t xml:space="preserve">Удаление зуба для взрослого</t>
         </is>
       </c>
       <c r="B16">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -333,7 +333,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Простое и сложное удаление зуба, под анестезией. Цена «от».</t>
+          <t xml:space="preserve">Удаление зуба для взрослого (простое и сложное), под анестезией. Цена «от».</t>
         </is>
       </c>
     </row>

--- a/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
@@ -700,11 +700,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Консультация детского стоматолога</t>
+          <t xml:space="preserve">Удаление молочного зуба</t>
         </is>
       </c>
       <c r="B35">
-        <v>1000</v>
+        <v>1650</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -713,38 +713,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
+          <t xml:space="preserve">Удаление молочного зуба у детей, бережно и без стресса. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: КТ + план лечения</t>
+          <t xml:space="preserve">Консультация детского стоматолога</t>
         </is>
       </c>
       <c r="B36">
-        <v>4200</v>
+        <v>1000</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
+          <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: отбеливание Amazing White</t>
+          <t xml:space="preserve">Акция: КТ + план лечения</t>
         </is>
       </c>
       <c r="B37">
-        <v>17500</v>
+        <v>4200</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -753,17 +753,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
+          <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: каждый 3-й имплант в подарок</t>
-        </is>
-      </c>
-      <c r="B38"/>
+          <t xml:space="preserve">Акция: отбеливание Amazing White</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>17500</v>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
@@ -771,14 +773,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
+          <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: чистка в подарок при имплантации или брекетах</t>
+          <t xml:space="preserve">Акция: каждый 3-й имплант в подарок</t>
         </is>
       </c>
       <c r="B39"/>
@@ -789,14 +791,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
+          <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Скидка 10% пенсионерам, многодетным и военнослужащим</t>
+          <t xml:space="preserve">Акция: чистка в подарок при имплантации или брекетах</t>
         </is>
       </c>
       <c r="B40"/>
@@ -807,14 +809,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
+          <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Семейная программа — скидка 3–10%</t>
+          <t xml:space="preserve">Скидка 10% пенсионерам, многодетным и военнослужащим</t>
         </is>
       </c>
       <c r="B41"/>
@@ -824,6 +826,24 @@
         </is>
       </c>
       <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Семейная программа — скидка 3–10%</t>
+        </is>
+      </c>
+      <c r="B42"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t xml:space="preserve">Скидка от 3% до 10% всем членам семьи при лечении 3 и более человек.</t>
         </is>

--- a/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
@@ -580,7 +580,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Комплексная гигиена (ультразвук + Air Flow + полировка + фторирование)</t>
+          <t xml:space="preserve">Комплексная гигиена (ультразвук + Air Flow + полировка)</t>
         </is>
       </c>
       <c r="B29">
@@ -593,7 +593,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Профессиональная чистка зубов: ультразвук, Air Flow, полировка, фторирование.</t>
+          <t xml:space="preserve">Профессиональная чистка зубов: ультразвук, Air Flow, полировка.</t>
         </is>
       </c>
     </row>

--- a/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
@@ -600,11 +600,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чистка Air Flow</t>
+          <t xml:space="preserve">Комплексная гигиена с брекетами</t>
         </is>
       </c>
       <c r="B30">
-        <v>3500</v>
+        <v>6000</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -613,98 +613,98 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чистка Air Flow — удаление налёта и пигмента.</t>
+          <t xml:space="preserve">Профессиональная чистка при установленной брекет-системе: ультразвук, Air Flow, полировка.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен Vector (1 челюсть)</t>
+          <t xml:space="preserve">Комплексная гигиена с ретейнерами</t>
         </is>
       </c>
       <c r="B31">
-        <v>8500</v>
+        <v>7000</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vector-терапия при пародонтите, 1 челюсть. Цена «от».</t>
+          <t xml:space="preserve">Профессиональная чистка при установленных ретейнерах: ультразвук, Air Flow, полировка.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plasmolifting (1 пробирка)</t>
+          <t xml:space="preserve">Чистка Air Flow</t>
         </is>
       </c>
       <c r="B32">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плазмолифтинг дёсен, 1 пробирка. Цена «от».</t>
+          <t xml:space="preserve">Чистка Air Flow — удаление налёта и пигмента.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение молочного зуба</t>
+          <t xml:space="preserve">Лечение дёсен Vector (1 челюсть)</t>
         </is>
       </c>
       <c r="B33">
-        <v>1500</v>
+        <v>8500</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Лечение дёсен</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение кариеса молочного зуба у детей с 2 лет, в игровой форме. Цена «от».</t>
+          <t xml:space="preserve">Vector-терапия при пародонтите, 1 челюсть. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цветная пломба Twinky Star</t>
+          <t xml:space="preserve">Plasmolifting (1 пробирка)</t>
         </is>
       </c>
       <c r="B34">
-        <v>2800</v>
+        <v>4500</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Лечение дёсен</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение молочного зуба с цветной пломбой Twinky Star. Цена «от».</t>
+          <t xml:space="preserve">Плазмолифтинг дёсен, 1 пробирка. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удаление молочного зуба</t>
+          <t xml:space="preserve">Лечение молочного зуба</t>
         </is>
       </c>
       <c r="B35">
-        <v>1650</v>
+        <v>1500</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -713,18 +713,18 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удаление молочного зуба у детей, бережно и без стресса. Цена «от».</t>
+          <t xml:space="preserve">Лечение кариеса молочного зуба у детей с 2 лет, в игровой форме. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Консультация детского стоматолога</t>
+          <t xml:space="preserve">Цветная пломба Twinky Star</t>
         </is>
       </c>
       <c r="B36">
-        <v>1000</v>
+        <v>2800</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -733,57 +733,59 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
+          <t xml:space="preserve">Лечение молочного зуба с цветной пломбой Twinky Star. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: КТ + план лечения</t>
+          <t xml:space="preserve">Удаление молочного зуба</t>
         </is>
       </c>
       <c r="B37">
-        <v>4200</v>
+        <v>1650</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
+          <t xml:space="preserve">Удаление молочного зуба у детей, бережно и без стресса. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: отбеливание Amazing White</t>
+          <t xml:space="preserve">Консультация детского стоматолога</t>
         </is>
       </c>
       <c r="B38">
-        <v>17500</v>
+        <v>1000</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
+          <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: каждый 3-й имплант в подарок</t>
-        </is>
-      </c>
-      <c r="B39"/>
+          <t xml:space="preserve">Акция: КТ + план лечения</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>4200</v>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
@@ -791,17 +793,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
+          <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: чистка в подарок при имплантации или брекетах</t>
-        </is>
-      </c>
-      <c r="B40"/>
+          <t xml:space="preserve">Акция: отбеливание Amazing White</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>17500</v>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
@@ -809,14 +813,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
+          <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Скидка 10% пенсионерам, многодетным и военнослужащим</t>
+          <t xml:space="preserve">Акция: каждый 3-й имплант в подарок</t>
         </is>
       </c>
       <c r="B41"/>
@@ -827,14 +831,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
+          <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Семейная программа — скидка 3–10%</t>
+          <t xml:space="preserve">Акция: чистка в подарок при имплантации или брекетах</t>
         </is>
       </c>
       <c r="B42"/>
@@ -844,6 +848,42 @@
         </is>
       </c>
       <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скидка 10% пенсионерам, многодетным и военнослужащим</t>
+        </is>
+      </c>
+      <c r="B43"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Семейная программа — скидка 3–10%</t>
+        </is>
+      </c>
+      <c r="B44"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t xml:space="preserve">Скидка от 3% до 10% всем членам семьи при лечении 3 и более человек.</t>
         </is>

--- a/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -660,206 +660,212 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен Vector (1 челюсть)</t>
+          <t xml:space="preserve">Ультразвуковая гигиена</t>
         </is>
       </c>
       <c r="B33">
-        <v>8500</v>
+        <v>2500</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vector-терапия при пародонтите, 1 челюсть. Цена «от».</t>
+          <t xml:space="preserve">Снятие зубного камня ультразвуком.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plasmolifting (1 пробирка)</t>
+          <t xml:space="preserve">Гигиена + глубокий кюретаж (карманы 3–4 мм)</t>
         </is>
       </c>
       <c r="B34">
-        <v>4500</v>
+        <v>7500</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение дёсен</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Плазмолифтинг дёсен, 1 пробирка. Цена «от».</t>
+          <t xml:space="preserve">Комплексная гигиена с глубоким кюретажем пародонтальных карманов 3–4 мм.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение молочного зуба</t>
+          <t xml:space="preserve">Гигиена + глубокий кюретаж (карманы от 5 мм)</t>
         </is>
       </c>
       <c r="B35">
-        <v>1500</v>
+        <v>9500</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение кариеса молочного зуба у детей с 2 лет, в игровой форме. Цена «от».</t>
+          <t xml:space="preserve">Комплексная гигиена с глубоким кюретажем пародонтальных карманов от 5 мм.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Цветная пломба Twinky Star</t>
+          <t xml:space="preserve">Глубокое фторирование</t>
         </is>
       </c>
       <c r="B36">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Гигиена</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лечение молочного зуба с цветной пломбой Twinky Star. Цена «от».</t>
+          <t xml:space="preserve">Укрепление эмали всех зубов: фторирующий гель в каппах.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удаление молочного зуба</t>
+          <t xml:space="preserve">Лечение дёсен Vector (1 челюсть)</t>
         </is>
       </c>
       <c r="B37">
-        <v>1650</v>
+        <v>8500</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Лечение дёсен</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удаление молочного зуба у детей, бережно и без стресса. Цена «от».</t>
+          <t xml:space="preserve">Vector-терапия при пародонтите, 1 челюсть. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Консультация детского стоматолога</t>
+          <t xml:space="preserve">Plasmolifting (1 пробирка)</t>
         </is>
       </c>
       <c r="B38">
-        <v>1000</v>
+        <v>4500</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Детская стоматология</t>
+          <t xml:space="preserve">Лечение дёсен</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
+          <t xml:space="preserve">Плазмолифтинг дёсен, 1 пробирка. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: КТ + план лечения</t>
+          <t xml:space="preserve">Лечение молочного зуба</t>
         </is>
       </c>
       <c r="B39">
-        <v>4200</v>
+        <v>1500</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
+          <t xml:space="preserve">Лечение кариеса молочного зуба у детей с 2 лет, в игровой форме. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: отбеливание Amazing White</t>
+          <t xml:space="preserve">Цветная пломба Twinky Star</t>
         </is>
       </c>
       <c r="B40">
-        <v>17500</v>
+        <v>2800</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
+          <t xml:space="preserve">Лечение молочного зуба с цветной пломбой Twinky Star. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: каждый 3-й имплант в подарок</t>
-        </is>
-      </c>
-      <c r="B41"/>
+          <t xml:space="preserve">Удаление молочного зуба</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>1650</v>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
+          <t xml:space="preserve">Удаление молочного зуба у детей, бережно и без стресса. Цена «от».</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акция: чистка в подарок при имплантации или брекетах</t>
-        </is>
-      </c>
-      <c r="B42"/>
+          <t xml:space="preserve">Консультация детского стоматолога</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>1000</v>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Акции</t>
+          <t xml:space="preserve">Детская стоматология</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
+          <t xml:space="preserve">Осмотр и план лечения у детского стоматолога.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Скидка 10% пенсионерам, многодетным и военнослужащим</t>
-        </is>
-      </c>
-      <c r="B43"/>
+          <t xml:space="preserve">Акция: КТ + план лечения</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>4200</v>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
@@ -867,23 +873,97 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
+          <t xml:space="preserve">Вместо 7 500 ₽. КТ двух челюстей, осмотр главврача, письменный план с фиксированными ценами на 30 дней. При договоре на лечение — бесплатно.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Акция: отбеливание Amazing White</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>17500</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вместо 25 000 ₽. Кабинетное отбеливание до 6–8 тонов за визит. Защита дёсен и реминерализация включены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акция: каждый 3-й имплант в подарок</t>
+        </is>
+      </c>
+      <c r="B45"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">При установке нескольких имплантов каждый третий — бесплатно. Гарантия 10 лет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акция: чистка в подарок при имплантации или брекетах</t>
+        </is>
+      </c>
+      <c r="B46"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Профгигиена (Air Flow + ультразвук + полировка) в подарок при договоре на имплантацию или брекеты. Экономия 5 000 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скидка 10% пенсионерам, многодетным и военнослужащим</t>
+        </is>
+      </c>
+      <c r="B47"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Акции</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скидка 10% на лечение, протезирование и гигиену по удостоверению. Действует постоянно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Семейная программа — скидка 3–10%</t>
         </is>
       </c>
-      <c r="B44"/>
-      <c r="C44" t="inlineStr">
+      <c r="B48"/>
+      <c r="C48" t="inlineStr">
         <is>
           <t xml:space="preserve">Акции</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t xml:space="preserve">Скидка от 3% до 10% всем членам семьи при лечении 3 и более человек.</t>
         </is>

--- a/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
+++ b/_materials/yandex-business/angel-dent-yandex-business-price.xlsx
@@ -680,7 +680,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Гигиена + глубокий кюретаж (карманы 3–4 мм)</t>
+          <t xml:space="preserve">Гигиена + чистка десневых карманов 3–4 мм (кюретаж)</t>
         </is>
       </c>
       <c r="B34">
@@ -700,7 +700,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Гигиена + глубокий кюретаж (карманы от 5 мм)</t>
+          <t xml:space="preserve">Гигиена + чистка десневых карманов от 5 мм (кюретаж)</t>
         </is>
       </c>
       <c r="B35">
